--- a/public/downloads/modelo_aura.xlsx
+++ b/public/downloads/modelo_aura.xlsx
@@ -1,59 +1,160 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Instruções" sheetId="1" r:id="rId1"/>
-    <sheet name="Produtos" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Instruções" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Produtos" state="visible" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="28">
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>📋 Instruções — Aura — Moda &amp; Vestuário</t>
+  </si>
+  <si>
+    <t>📌 Como preencher esta planilha:</t>
+  </si>
+  <si>
+    <t>1. Vá até a aba "Produtos" (ao lado).</t>
+  </si>
+  <si>
+    <t>2. Substitua os dados de exemplo pelos seus produtos.</t>
+  </si>
+  <si>
+    <t>3. Mantenha os cabeçalhos exatamente como estão (linha 1).</t>
+  </si>
+  <si>
+    <t>4. As células com fundo cinza claro (linhas 2 em diante) são onde você deve digitar.</t>
+  </si>
+  <si>
+    <t>5. Na coluna Preço, digite apenas números (ex: 29.90).</t>
+  </si>
+  <si>
+    <t>6. Na coluna "Tamanhos (P, M, G)", use valores separados por vírgula se houver múltiplas opções.</t>
+  </si>
+  <si>
+    <t>7. Após preencher, faça upload da planilha no site ZapCatálogo.</t>
+  </si>
+  <si>
+    <t>✅ Importante: não altere os nomes das colunas na aba Produtos.</t>
+  </si>
+  <si>
+    <t>Nome do Produto</t>
+  </si>
+  <si>
+    <t>Preço</t>
+  </si>
+  <si>
+    <t>Descrição</t>
+  </si>
+  <si>
+    <t>Categoria/Tag</t>
+  </si>
+  <si>
+    <t>Tamanhos (P, M, G)</t>
+  </si>
+  <si>
+    <t>Blusa Silk Blend</t>
+  </si>
+  <si>
+    <t>Seda ecológica · Gola V</t>
+  </si>
+  <si>
+    <t>Premium</t>
+  </si>
+  <si>
+    <t>P,M,G,GG</t>
+  </si>
+  <si>
+    <t>Calça Jeans Premium</t>
+  </si>
+  <si>
+    <t>Algodão orgânico · Comfort Fit</t>
+  </si>
+  <si>
+    <t>Novo</t>
+  </si>
+  <si>
+    <t>38,40,42,44</t>
+  </si>
+  <si>
+    <t>Vestido Floral Verão</t>
+  </si>
+  <si>
+    <t>Viscose · Estampado floral</t>
+  </si>
+  <si>
+    <t>P,M,G</t>
+  </si>
+  <si>
+    <t>⬆ Preencha acima com seus produtos (substitua os exemplos)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1A5276"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1A5276"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF888888"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A5276"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9F9F9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -61,18 +162,72 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF888888"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE0E0E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,255 +552,1026 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="50.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="1" max="1" width="55" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Informação</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Detalhe</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Instruções de preenchimento</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v/>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Modelo</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Aura — Moda &amp; Vestuário</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>1. Preencha a aba "Produtos" com seus itens.</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>2. A coluna Tamanhos pode conter valores separados por vírgula (ex: P,M,G) ou "Único".</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>3. A coluna Imagem aceita URLs públicas de imagem.</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>4. Não altere os nomes das colunas.</v>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>5. Após preencher, faça upload da planilha no site.</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
-  </ignoredErrors>
+  <mergeCells count="1">
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E52"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="40.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="50.83203125" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nome</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Preço</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Descrição</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Tag</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Tamanhos</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Imagem</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Calça Jeans Premium</v>
-      </c>
-      <c r="B2">
+    <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="5">
+        <v>129.9</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="5">
         <v>189.9</v>
       </c>
-      <c r="C2" t="str">
-        <v>Algodão orgânico · Comfort Fit</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Novo</v>
-      </c>
-      <c r="E2" t="str">
-        <v>38,40,42,44</v>
-      </c>
-      <c r="F2" t="str">
-        <v>https://images.unsplash.com/photo-1542272604-787c3835535d?w=400</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Blusa Silk Blend</v>
-      </c>
-      <c r="B3">
-        <v>129.9</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Seda ecológica · Gola V</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="E3" t="str">
-        <v>P,M,G,GG</v>
-      </c>
-      <c r="F3" t="str">
-        <v>https://images.unsplash.com/photo-1554568218-0f1715e72254?w=400</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Sapatilha Comfort</v>
-      </c>
-      <c r="B4">
-        <v>159.9</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Couro legítimo · Palmilha ortopédica</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Promoção</v>
-      </c>
-      <c r="E4" t="str">
-        <v>34,35,36,37,38</v>
-      </c>
-      <c r="F4" t="str">
-        <v>https://images.unsplash.com/photo-1595950653106-6c9ebd614d3a?w=400</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Bolsa Tote Couro</v>
-      </c>
-      <c r="B5">
-        <v>249.9</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Couro legítimo · Média</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Essencial</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Único</v>
-      </c>
-      <c r="F5" t="str">
-        <v>https://images.unsplash.com/photo-1584917865442-de89df76afd3?w=400</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Vestido Floral Verão</v>
-      </c>
-      <c r="B6">
+      <c r="C3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="5">
         <v>179.9</v>
       </c>
-      <c r="C6" t="str">
-        <v>Viscose · Estampado</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Novo</v>
-      </c>
-      <c r="E6" t="str">
-        <v>P,M,G</v>
-      </c>
-      <c r="F6" t="str">
-        <v>https://images.unsplash.com/photo-1572804013309-59a88b7e2181?w=400</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Cinto Couro Legítimo</v>
-      </c>
-      <c r="B7">
-        <v>89.9</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Couro · Fivela dourada</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Acessório</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Único</v>
-      </c>
-      <c r="F7" t="str">
-        <v>https://images.unsplash.com/photo-1553062407-98eeb64c6a62?w=400</v>
-      </c>
+      <c r="C4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
-  </ignoredErrors>
+  <mergeCells count="1">
+    <mergeCell ref="A52:E52"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>